--- a/DATA/DGPMV GUATEMALA-HONDURAS.xlsx
+++ b/DATA/DGPMV GUATEMALA-HONDURAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf48b3f04032ef9d/Documentos/SERVICIOS/PARKA/MIGRACIÓN/OFICINA/ALEX/IA-NAMI/BASES/DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4547993-FCE8-49E2-99C6-C2F0F74274DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{E4547993-FCE8-49E2-99C6-C2F0F74274DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5A846FD-E70A-40C9-A4C4-F204CA16AFD0}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="5265" windowWidth="29040" windowHeight="15720" xr2:uid="{15D724FD-5320-46C9-956E-FC942EB20753}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{15D724FD-5320-46C9-956E-FC942EB20753}"/>
   </bookViews>
   <sheets>
     <sheet name="GUATEMALA Y HONDURAS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="13">
   <si>
     <t>DIA</t>
   </si>
@@ -120,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -294,33 +294,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -356,12 +334,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3144EFAC-2C53-4F33-8B98-DA5319F435D0}">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.73046875" bestFit="1" customWidth="1"/>
@@ -2731,19 +2703,48 @@
       <c r="D71" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="11">
         <v>70</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="11">
         <v>70</v>
       </c>
-      <c r="G71" s="13">
-        <v>0</v>
-      </c>
-      <c r="H71" s="13">
-        <v>0</v>
-      </c>
-      <c r="I71" s="14">
+      <c r="G71" s="11">
+        <v>0</v>
+      </c>
+      <c r="H71" s="11">
+        <v>0</v>
+      </c>
+      <c r="I71" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A72" s="10">
+        <v>46293</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="11">
+        <v>37</v>
+      </c>
+      <c r="F72" s="11">
+        <v>37</v>
+      </c>
+      <c r="G72" s="11">
+        <v>0</v>
+      </c>
+      <c r="H72" s="11">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12">
         <v>0</v>
       </c>
     </row>
